--- a/output/xlsx/CRUDDocumentos--GT-.xlsx
+++ b/output/xlsx/CRUDDocumentos--GT-.xlsx
@@ -107,10 +107,10 @@
     <t>exibe lista completa de documentos</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe página com campos de cadastro de novo documento</t>
-  </si>
-  <si>
-    <t>exibe página com campos de cadastro de novo documento</t>
+    <t>system: SYSTEM: exibe pagina com campos de cadastro de novo documento</t>
+  </si>
+  <si>
+    <t>exibe pagina com campos de cadastro de novo documento</t>
   </si>
   <si>
     <t>system: SYSTEM: exibe lista de documentos</t>
@@ -137,10 +137,10 @@
     <t>exibe dados do documento</t>
   </si>
   <si>
-    <t>system: SYSTEM: se existir extração da familia cadastrada, esta deve exibir no campo Document um link para o novo documento</t>
-  </si>
-  <si>
-    <t>se existir extração da familia cadastrada, esta deve exibir no campo Document um link para o novo documento</t>
+    <t>system: SYSTEM: se existir extracao da familia cadastrada, esta deve exibir no campo Document um link para o novo documento</t>
+  </si>
+  <si>
+    <t>se existir extracao da familia cadastrada, esta deve exibir no campo Document um link para o novo documento</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>

--- a/output/xlsx/CRUDDocumentos--GT-.xlsx
+++ b/output/xlsx/CRUDDocumentos--GT-.xlsx
@@ -107,10 +107,10 @@
     <t>exibe lista completa de documentos</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe pagina com campos de cadastro de novo documento</t>
-  </si>
-  <si>
-    <t>exibe pagina com campos de cadastro de novo documento</t>
+    <t>system: SYSTEM: exibe página com campos de cadastro de novo documento</t>
+  </si>
+  <si>
+    <t>exibe página com campos de cadastro de novo documento</t>
   </si>
   <si>
     <t>system: SYSTEM: exibe lista de documentos</t>
@@ -137,10 +137,10 @@
     <t>exibe dados do documento</t>
   </si>
   <si>
-    <t>system: SYSTEM: se existir extracao da familia cadastrada, esta deve exibir no campo Document um link para o novo documento</t>
-  </si>
-  <si>
-    <t>se existir extracao da familia cadastrada, esta deve exibir no campo Document um link para o novo documento</t>
+    <t>system: SYSTEM: se existir extração da familia cadastrada, esta deve exibir no campo Document um link para o novo documento</t>
+  </si>
+  <si>
+    <t>se existir extração da familia cadastrada, esta deve exibir no campo Document um link para o novo documento</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -152,10 +152,10 @@
     <t>Alternative Flow 1: Faltando arquivo</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe mensagem informando que os dados não correspondem a formatação esperada ou esta faltando informacoes</t>
-  </si>
-  <si>
-    <t>exibe mensagem informando que os dados não correspondem a formatação esperada ou esta faltando informacoes</t>
+    <t>system: SYSTEM: exibe mensagem informando que os dados não correspondem a formatação esperada ou está faltando informações</t>
+  </si>
+  <si>
+    <t>exibe mensagem informando que os dados não correspondem a formatação esperada ou está faltando informações</t>
   </si>
   <si>
     <t>TC3</t>
@@ -173,13 +173,13 @@
     <t>TC4</t>
   </si>
   <si>
-    <t>Alternative Flow 7: Upload de arquivo nao pdf</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: exibe mensagem informando que o documento especificado nao e um arquivo PDF</t>
-  </si>
-  <si>
-    <t>exibe mensagem informando que o documento especificado nao e um arquivo PDF</t>
+    <t>Alternative Flow 7: Upload de arquivo não pdf</t>
+  </si>
+  <si>
+    <t>system: SYSTEM: exibe mensagem informando que o documento especificado não é um arquivo PDF</t>
+  </si>
+  <si>
+    <t>exibe mensagem informando que o documento especificado não é um arquivo PDF</t>
   </si>
   <si>
     <t>TC6</t>
@@ -200,16 +200,16 @@
     <t>Alternative Flow 4: Deleta documento</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe mensagem solicitando confirmacao</t>
-  </si>
-  <si>
-    <t>exibe mensagem solicitando confirmacao</t>
+    <t>system: SYSTEM: exibe mensagem solicitando confirmação</t>
+  </si>
+  <si>
+    <t>exibe mensagem solicitando confirmação</t>
   </si>
   <si>
     <t>TC8</t>
   </si>
   <si>
-    <t>Alternative Flow 5: Visualizacao para Operador, Gerente</t>
+    <t>Alternative Flow 5: Visualização para Operador, Gerente</t>
   </si>
   <si>
     <t>system: SYSTEM: exibe lista de documentos pertencentes ao mesmo laboratório do usuário</t>
